--- a/data/credit_bond_2026-09-17.xlsx
+++ b/data/credit_bond_2026-09-17.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9100</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -783,7 +783,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>2.01%~2.11%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -920,7 +924,11 @@
           <t>09-17 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>012682294.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -959,7 +967,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2400/2.2200</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -999,7 +1007,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.25%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1179,7 +1191,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9600/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1219,7 +1231,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>AA+</t>

--- a/data/credit_bond_2026-09-17.xlsx
+++ b/data/credit_bond_2026-09-17.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-17" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-18" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-17</t>
+          <t>数据来源：DM    2026-09-18</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C 27.03</t>
+          <t>C- 24.70</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.2555</t>
+          <t>2.2575</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 35.99</t>
+          <t>B- 36.47</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1135,7 +1135,9 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1145,7 +1147,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1201,7 +1203,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C 27.03</t>
+          <t>C- 24.70</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-17.xlsx
+++ b/data/credit_bond_2026-09-17.xlsx
@@ -719,8 +719,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>75.94</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -937,14 +941,20 @@
       <c r="E4" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.94 ~ 2.24</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>103.33</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -1169,8 +1179,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>37.94</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.82</t>

--- a/data/credit_bond_2026-09-17.xlsx
+++ b/data/credit_bond_2026-09-17.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-18" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-21" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-18</t>
+          <t>数据来源：DM    2026-09-21</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 24.70</t>
+          <t>C- 23.17</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 36.47</t>
+          <t>B- 37.61</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1010,7 +1010,9 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>0.99</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1217,7 +1219,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 24.70</t>
+          <t>C- 23.17</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-17.xlsx
+++ b/data/credit_bond_2026-09-17.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-21" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-22" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 23.17</t>
+          <t>C- 23.35</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 37.61</t>
+          <t>B- 38.83</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 23.17</t>
+          <t>C- 23.35</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-17.xlsx
+++ b/data/credit_bond_2026-09-17.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-22" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-23" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
     </row>
@@ -692,72 +692,74 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26长开05</t>
+          <t>26华发集团SCP008</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>09-17 19:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>284048.SH</t>
+          <t>012682294.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.94 ~ 2.24</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>75.94</v>
+        <v>103.33</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25长寿开投PPN001A</t>
+          <t>24珠华01</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>3.35Y</t>
+          <t>270D+2.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.9288</t>
+          <t>2.2575</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/1.9100</t>
+          <t>2.2400/2.2200</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 23.35</t>
+          <t>B- 36.11</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -767,7 +769,7 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>09-17 15:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -777,46 +779,48 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="U3" s="3"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.99</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>2.01%~2.11%</t>
+          <t>2.21%~2.25%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金[26长开01,23长开07,23长开09]</t>
+          <t>本期超短期融资券发行规模为10亿元,用于偿还发行人本部债务融资工具本金[21华发集团MTN010(乡村振兴)]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -826,28 +830,28 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种一)</t>
+          <t>珠海华发集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2027-06-15</t>
         </is>
       </c>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -857,37 +861,37 @@
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -915,79 +919,81 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26华发集团SCP008</t>
+          <t>26长开06</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>012682294.IB</t>
+          <t>284049.SH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2+2+1</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.94 ~ 2.24</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>103.33</v>
+        <v>37.94</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>24珠华01</t>
+          <t>24长寿开投PPN001</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>270D+2.00Y</t>
+          <t>2.35Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.2575</t>
+          <t>1.8412</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2.2400/2.2200</t>
+          <t>1.9600/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>重庆长寿开发投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 38.83</t>
+          <t>C- 22.40</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -997,7 +1003,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 15:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1007,48 +1013,48 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.99</v>
+        <v>3.7667</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.25%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为10亿元,用于偿还发行人本部债务融资工具本金[21华发集团MTN010(乡村振兴)]</t>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金[26长开01,23长开07,23长开09]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司</t>
+          <t>华源证券股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1058,28 +1064,28 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年度第八期超短期融资券</t>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2027-06-15</t>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1089,42 +1095,42 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-22</t>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
@@ -1134,7 +1140,7 @@
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">
@@ -1147,14 +1153,12 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26长开06</t>
+          <t>26长开05</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1164,52 +1168,54 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>284049.SH</t>
+          <t>284048.SH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2+2+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>37.94</v>
+        <v>75.94</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>24长寿开投PPN001</t>
+          <t>25长寿开投PPN001A</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.35Y</t>
+          <t>3.35Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.8412</t>
+          <t>1.9288</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.9600/--</t>
+          <t>--/1.9100</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1219,7 +1225,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 23.35</t>
+          <t>C- 22.40</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1242,7 +1248,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>4.0667</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1251,7 +1259,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>2.01%~2.11%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1293,7 +1301,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种二)</t>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1354,7 +1362,7 @@
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>2028-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AV5" s="3" t="inlineStr">
@@ -1364,7 +1372,7 @@
       </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX5" s="3" t="inlineStr">
